--- a/Proyecto_CBC/PMA.xlsx
+++ b/Proyecto_CBC/PMA.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
